--- a/INNOSTAT_Metadata_DataSource.xlsx
+++ b/INNOSTAT_Metadata_DataSource.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\EAS_INNOV\results\2025\5.Dissemination\INNOSTAT package ver 15 Apr 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\EAS_INNOV\results\2025\5.Dissemination\INNOSTAT package (backup old metadata pdfs)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AEB1A9-4016-4E0F-803D-FF591C8AEB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDE3481-B40C-4CCE-AEE3-6DD5911E7BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{53FD16E5-815B-47BC-B09D-BBC15F109EB4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{53FD16E5-815B-47BC-B09D-BBC15F109EB4}"/>
   </bookViews>
   <sheets>
     <sheet name="2021 round" sheetId="3" r:id="rId1"/>
@@ -3224,6 +3224,9 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3259,9 +3262,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4268,31 +4268,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{726EBBA4-C312-4EA6-9C5B-721D6A5B392E}">
   <dimension ref="B1:F39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="61.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="3" max="3" width="61.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="46" t="s">
         <v>766</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="19"/>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="48"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="50"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="51"/>
       <c r="F2" s="20"/>
     </row>
-    <row r="3" spans="2:6" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="21" t="s">
         <v>763</v>
       </c>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F3" s="24"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="25" t="s">
         <v>1</v>
       </c>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="29" t="s">
         <v>2</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="F5" s="28"/>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="32" t="s">
         <v>3</v>
       </c>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="32" t="s">
         <v>5</v>
       </c>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="F7" s="28"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="32" t="s">
         <v>7</v>
       </c>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="F8" s="28"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="32" t="s">
         <v>8</v>
       </c>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F9" s="28"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="32" t="s">
         <v>802</v>
       </c>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F10" s="28"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="32" t="s">
         <v>9</v>
       </c>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F11" s="28"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="32" t="s">
         <v>10</v>
       </c>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="F12" s="28"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="32" t="s">
         <v>11</v>
       </c>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="F13" s="28"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="32" t="s">
         <v>12</v>
       </c>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F14" s="28"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="32" t="s">
         <v>13</v>
       </c>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F15" s="28"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="32" t="s">
         <v>14</v>
       </c>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="F16" s="28"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="32" t="s">
         <v>15</v>
       </c>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="F17" s="28"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="32" t="s">
         <v>16</v>
       </c>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="F18" s="28"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="32" t="s">
         <v>17</v>
       </c>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F19" s="28"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="32" t="s">
         <v>19</v>
       </c>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F20" s="28"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="32" t="s">
         <v>20</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="F21" s="28"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="32" t="s">
         <v>21</v>
       </c>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="F22" s="28"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="32" t="s">
         <v>22</v>
       </c>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="F23" s="28"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="32" t="s">
         <v>23</v>
       </c>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F24" s="28"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="32" t="s">
         <v>25</v>
       </c>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="F25" s="28"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="32" t="s">
         <v>26</v>
       </c>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="F26" s="28"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="32" t="s">
         <v>27</v>
       </c>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="F27" s="28"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="32" t="s">
         <v>28</v>
       </c>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F28" s="28"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="32" t="s">
         <v>790</v>
       </c>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F29" s="28"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="32" t="s">
         <v>29</v>
       </c>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F30" s="28"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="32" t="s">
         <v>30</v>
       </c>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="F31" s="28"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="32" t="s">
         <v>32</v>
       </c>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F32" s="28"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="32" t="s">
         <v>33</v>
       </c>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="F33" s="28"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="32" t="s">
         <v>34</v>
       </c>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F34" s="28"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B35" s="32" t="s">
         <v>35</v>
       </c>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="F35" s="28"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="32" t="s">
         <v>791</v>
       </c>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F36" s="28"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="36" t="s">
         <v>36</v>
       </c>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="F37" s="28"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="6" t="s">
         <v>793</v>
       </c>
       <c r="D39" s="18" t="str">
-        <f>HYPERLINK("https://stats.oecd.org/wbos/fileview2.aspx?IDFile=253b7b6d-50d7-4aa9-a1ce-679dbdedff52","Click here")</f>
+        <f>HYPERLINK("https://raw.githubusercontent.com/STIScoreboard/INNOSTAT/main/Metadata Innovation Indicators 2016-2018.pdf","Click here")</f>
         <v>Click here</v>
       </c>
     </row>
@@ -4832,35 +4832,38 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial Narrow"&amp;10&amp;K0000FF Unclassified - Non classifié</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E668476E-3974-4ECE-BDED-94A8EF19204F}">
   <dimension ref="B1:E44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="61.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="3" max="3" width="61.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="51" t="s">
+    <row r="1" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="52" t="s">
         <v>766</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="56"/>
-    </row>
-    <row r="3" spans="2:5" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
+    </row>
+    <row r="3" spans="2:5" ht="35" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>763</v>
       </c>
@@ -4874,7 +4877,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
@@ -4902,7 +4905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
@@ -4916,7 +4919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="11" t="s">
         <v>4</v>
       </c>
@@ -4930,7 +4933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
@@ -4944,7 +4947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="11" t="s">
         <v>7</v>
       </c>
@@ -4958,7 +4961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="11" t="s">
         <v>8</v>
       </c>
@@ -4972,7 +4975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="11" t="s">
         <v>779</v>
       </c>
@@ -4986,7 +4989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
@@ -5000,7 +5003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="11" t="s">
         <v>10</v>
       </c>
@@ -5014,7 +5017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
@@ -5028,7 +5031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
@@ -5042,7 +5045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
         <v>13</v>
       </c>
@@ -5056,7 +5059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="11" t="s">
         <v>14</v>
       </c>
@@ -5070,7 +5073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="11" t="s">
         <v>15</v>
       </c>
@@ -5084,7 +5087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="11" t="s">
         <v>16</v>
       </c>
@@ -5098,7 +5101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="11" t="s">
         <v>17</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="11" t="s">
         <v>18</v>
       </c>
@@ -5126,7 +5129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="11" t="s">
         <v>19</v>
       </c>
@@ -5140,7 +5143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="11" t="s">
         <v>782</v>
       </c>
@@ -5154,7 +5157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="11" t="s">
         <v>20</v>
       </c>
@@ -5168,7 +5171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="11" t="s">
         <v>21</v>
       </c>
@@ -5182,7 +5185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="11" t="s">
         <v>22</v>
       </c>
@@ -5196,7 +5199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="11" t="s">
         <v>23</v>
       </c>
@@ -5210,7 +5213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="11" t="s">
         <v>24</v>
       </c>
@@ -5224,7 +5227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="11" t="s">
         <v>25</v>
       </c>
@@ -5238,7 +5241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="11" t="s">
         <v>26</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="11" t="s">
         <v>27</v>
       </c>
@@ -5266,7 +5269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="11" t="s">
         <v>789</v>
       </c>
@@ -5280,7 +5283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="11" t="s">
         <v>28</v>
       </c>
@@ -5294,7 +5297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="11" t="s">
         <v>790</v>
       </c>
@@ -5308,7 +5311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="11" t="s">
         <v>29</v>
       </c>
@@ -5322,7 +5325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="11" t="s">
         <v>30</v>
       </c>
@@ -5336,7 +5339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="11" t="s">
         <v>31</v>
       </c>
@@ -5350,7 +5353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B38" s="11" t="s">
         <v>32</v>
       </c>
@@ -5364,7 +5367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39" s="11" t="s">
         <v>33</v>
       </c>
@@ -5378,7 +5381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40" s="11" t="s">
         <v>34</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="11" t="s">
         <v>35</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42" s="14" t="s">
         <v>791</v>
       </c>
@@ -5420,12 +5423,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B44" s="6" t="s">
         <v>793</v>
       </c>
       <c r="D44" s="18" t="str">
-        <f>HYPERLINK("https://stats.oecd.org/wbos/fileview2.aspx?IDFile=fc8d0e70-31da-4081-9a11-7fd29be75a0d","Click here")</f>
+        <f>HYPERLINK("https://raw.githubusercontent.com/STIScoreboard/INNOSTAT/main/OECD_Metadata_Innovation_Indicators_2018-2020.pdf","Click here")</f>
         <v>Click here</v>
       </c>
     </row>
@@ -5435,53 +5438,56 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial Narrow"&amp;10&amp;K0000FF Unclassified - Non classifié</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62FB3C8-8EFB-4B61-A96C-DD62F06F83CA}">
   <dimension ref="A1:AM41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="46.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="32.28515625" customWidth="1"/>
-    <col min="10" max="10" width="51.28515625" customWidth="1"/>
-    <col min="11" max="11" width="73.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="13" width="24.7109375" customWidth="1"/>
-    <col min="14" max="14" width="35.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" customWidth="1"/>
+    <col min="6" max="6" width="46.453125" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" customWidth="1"/>
+    <col min="9" max="9" width="32.26953125" customWidth="1"/>
+    <col min="10" max="10" width="51.26953125" customWidth="1"/>
+    <col min="11" max="11" width="73.453125" customWidth="1"/>
+    <col min="12" max="12" width="18.1796875" customWidth="1"/>
+    <col min="13" max="13" width="24.7265625" customWidth="1"/>
+    <col min="14" max="14" width="35.1796875" customWidth="1"/>
     <col min="15" max="15" width="32" customWidth="1"/>
     <col min="16" max="16" width="48" customWidth="1"/>
-    <col min="17" max="17" width="63.85546875" customWidth="1"/>
-    <col min="18" max="18" width="18.5703125" customWidth="1"/>
-    <col min="19" max="19" width="21.7109375" customWidth="1"/>
-    <col min="20" max="20" width="24.42578125" customWidth="1"/>
-    <col min="21" max="21" width="70.85546875" customWidth="1"/>
-    <col min="22" max="22" width="55.28515625" customWidth="1"/>
-    <col min="23" max="23" width="18.5703125" customWidth="1"/>
-    <col min="24" max="24" width="40.85546875" customWidth="1"/>
-    <col min="25" max="25" width="19.140625" customWidth="1"/>
-    <col min="26" max="26" width="33.5703125" customWidth="1"/>
-    <col min="27" max="27" width="27.7109375" customWidth="1"/>
-    <col min="28" max="30" width="25.5703125" customWidth="1"/>
-    <col min="31" max="32" width="15.5703125" customWidth="1"/>
-    <col min="33" max="33" width="47.7109375" customWidth="1"/>
-    <col min="34" max="34" width="58.28515625" customWidth="1"/>
+    <col min="17" max="17" width="63.81640625" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" customWidth="1"/>
+    <col min="19" max="19" width="21.7265625" customWidth="1"/>
+    <col min="20" max="20" width="24.453125" customWidth="1"/>
+    <col min="21" max="21" width="70.81640625" customWidth="1"/>
+    <col min="22" max="22" width="55.26953125" customWidth="1"/>
+    <col min="23" max="23" width="18.54296875" customWidth="1"/>
+    <col min="24" max="24" width="40.81640625" customWidth="1"/>
+    <col min="25" max="25" width="19.1796875" customWidth="1"/>
+    <col min="26" max="26" width="33.54296875" customWidth="1"/>
+    <col min="27" max="27" width="27.7265625" customWidth="1"/>
+    <col min="28" max="30" width="25.54296875" customWidth="1"/>
+    <col min="31" max="32" width="15.54296875" customWidth="1"/>
+    <col min="33" max="33" width="47.7265625" customWidth="1"/>
+    <col min="34" max="34" width="58.26953125" customWidth="1"/>
     <col min="35" max="35" width="38" customWidth="1"/>
-    <col min="36" max="36" width="30.7109375" customWidth="1"/>
-    <col min="37" max="37" width="67.5703125" customWidth="1"/>
-    <col min="38" max="38" width="28.28515625" customWidth="1"/>
-    <col min="39" max="39" width="73.42578125" customWidth="1"/>
+    <col min="36" max="36" width="30.7265625" customWidth="1"/>
+    <col min="37" max="37" width="67.54296875" customWidth="1"/>
+    <col min="38" max="38" width="28.26953125" customWidth="1"/>
+    <col min="39" max="39" width="73.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="1" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" s="1" customFormat="1" ht="56" x14ac:dyDescent="0.35">
       <c r="A1" s="40" t="s">
         <v>763</v>
       </c>
@@ -5600,7 +5606,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="57" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="42" x14ac:dyDescent="0.35">
       <c r="A2" s="40" t="s">
         <v>726</v>
       </c>
@@ -5719,7 +5725,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="294" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">
         <v>727</v>
       </c>
@@ -5838,7 +5844,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A4" s="40" t="s">
         <v>728</v>
       </c>
@@ -5957,7 +5963,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="140" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>729</v>
       </c>
@@ -6076,7 +6082,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="126" x14ac:dyDescent="0.35">
       <c r="A6" s="40" t="s">
         <v>731</v>
       </c>
@@ -6195,7 +6201,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="171" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="154" x14ac:dyDescent="0.35">
       <c r="A7" s="40" t="s">
         <v>730</v>
       </c>
@@ -6314,7 +6320,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="270.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="238" x14ac:dyDescent="0.35">
       <c r="A8" s="40" t="s">
         <v>732</v>
       </c>
@@ -6433,7 +6439,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="112" x14ac:dyDescent="0.35">
       <c r="A9" s="40" t="s">
         <v>734</v>
       </c>
@@ -6552,7 +6558,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A10" s="40" t="s">
         <v>839</v>
       </c>
@@ -6671,7 +6677,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="128.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="112" x14ac:dyDescent="0.35">
       <c r="A11" s="40" t="s">
         <v>826</v>
       </c>
@@ -6790,7 +6796,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="70" x14ac:dyDescent="0.35">
       <c r="A12" s="40" t="s">
         <v>744</v>
       </c>
@@ -6909,7 +6915,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A13" s="40" t="s">
         <v>735</v>
       </c>
@@ -7028,7 +7034,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="112" x14ac:dyDescent="0.35">
       <c r="A14" s="40" t="s">
         <v>737</v>
       </c>
@@ -7147,7 +7153,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="112" x14ac:dyDescent="0.35">
       <c r="A15" s="40" t="s">
         <v>739</v>
       </c>
@@ -7266,7 +7272,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="126" x14ac:dyDescent="0.35">
       <c r="A16" s="40" t="s">
         <v>740</v>
       </c>
@@ -7385,7 +7391,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A17" s="40" t="s">
         <v>741</v>
       </c>
@@ -7504,7 +7510,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="327.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="294" x14ac:dyDescent="0.35">
       <c r="A18" s="40" t="s">
         <v>736</v>
       </c>
@@ -7623,7 +7629,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="256.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="224" x14ac:dyDescent="0.35">
       <c r="A19" s="40" t="s">
         <v>743</v>
       </c>
@@ -7742,7 +7748,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="171" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="154" x14ac:dyDescent="0.35">
       <c r="A20" s="40" t="s">
         <v>745</v>
       </c>
@@ -7861,7 +7867,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A21" s="40" t="s">
         <v>747</v>
       </c>
@@ -7980,7 +7986,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="112" x14ac:dyDescent="0.35">
       <c r="A22" s="40" t="s">
         <v>746</v>
       </c>
@@ -8099,7 +8105,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A23" s="40" t="s">
         <v>748</v>
       </c>
@@ -8218,7 +8224,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A24" s="40" t="s">
         <v>749</v>
       </c>
@@ -8337,7 +8343,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="182" x14ac:dyDescent="0.35">
       <c r="A25" s="40" t="s">
         <v>750</v>
       </c>
@@ -8456,7 +8462,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="128.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="112" x14ac:dyDescent="0.35">
       <c r="A26" s="40" t="s">
         <v>753</v>
       </c>
@@ -8575,7 +8581,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="224" x14ac:dyDescent="0.35">
       <c r="A27" s="40" t="s">
         <v>751</v>
       </c>
@@ -8694,7 +8700,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="182" x14ac:dyDescent="0.35">
       <c r="A28" s="40" t="s">
         <v>752</v>
       </c>
@@ -8813,7 +8819,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A29" s="40" t="s">
         <v>754</v>
       </c>
@@ -8932,7 +8938,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="171" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="140" x14ac:dyDescent="0.35">
       <c r="A30" s="40" t="s">
         <v>755</v>
       </c>
@@ -9051,7 +9057,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="171" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="140" x14ac:dyDescent="0.35">
       <c r="A31" s="40" t="s">
         <v>756</v>
       </c>
@@ -9170,7 +9176,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="327.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="294" x14ac:dyDescent="0.35">
       <c r="A32" s="40" t="s">
         <v>757</v>
       </c>
@@ -9289,7 +9295,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="126" x14ac:dyDescent="0.35">
       <c r="A33" s="40" t="s">
         <v>758</v>
       </c>
@@ -9408,7 +9414,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="34" spans="1:39" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A34" s="40" t="s">
         <v>759</v>
       </c>
@@ -9527,7 +9533,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="35" spans="1:39" ht="399" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="350" x14ac:dyDescent="0.35">
       <c r="A35" s="40" t="s">
         <v>762</v>
       </c>
@@ -9646,7 +9652,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="36" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A36" s="40" t="s">
         <v>738</v>
       </c>
@@ -9765,7 +9771,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="356.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="322" x14ac:dyDescent="0.35">
       <c r="A37" s="40" t="s">
         <v>760</v>
       </c>
@@ -9884,7 +9890,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="38" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A38" s="40" t="s">
         <v>733</v>
       </c>
@@ -10003,7 +10009,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="39" spans="1:39" ht="114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="98" x14ac:dyDescent="0.35">
       <c r="A39" s="40" t="s">
         <v>761</v>
       </c>
@@ -10122,7 +10128,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="40" spans="1:39" ht="171" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="168" x14ac:dyDescent="0.35">
       <c r="A40" s="40" t="s">
         <v>742</v>
       </c>
@@ -10241,7 +10247,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="41" spans="1:39" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="84" x14ac:dyDescent="0.35">
       <c r="A41" s="40" t="s">
         <v>860</v>
       </c>
@@ -10356,14 +10362,14 @@
       <c r="AL41" s="40" t="s">
         <v>673</v>
       </c>
-      <c r="AM41" s="57" t="s">
+      <c r="AM41" s="45" t="s">
         <v>673</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K0000FF Restricted Use - À usage restreint</oddFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial Narrow"&amp;10&amp;K0000FF Unclassified - Non classifié</oddFooter>
   </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
